--- a/光伏配储项目/电价数据/2026/古井站.xlsx
+++ b/光伏配储项目/电价数据/2026/古井站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.53843</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.37995</v>
+      </c>
+      <c r="C117" t="n">
+        <v>1.26308</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.64663</v>
+      </c>
+      <c r="E117" t="n">
+        <v>1.02535</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.8339099999999999</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.7236699999999999</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.44051</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45617</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.44051</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42258</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.45538</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.40816</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.39764</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.3985</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38319</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40145</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.4245</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41089</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35277</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39174</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38412</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41529</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39391</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42665</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41225</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42225</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41219</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44584</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.47885</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.31562</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.34051</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.30004</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.32414</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.37415</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.7787200000000001</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.62283</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.53244</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.27694</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.4042</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.58936</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.6150099999999999</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.27816</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.34051</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.84333</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.8456900000000001</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.85719</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.52022</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.17933</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.56232</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.33199</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.31794</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.33944</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.3528</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.56024</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.83194</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.9660700000000001</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.33832</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.61934</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.32066</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.66923</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.64632</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.82341</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.7726000000000001</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.83968</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>1.08704</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>1.34527</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>1.49572</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>1.77166</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.67065</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.18968</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>1.00805</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.86485</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>1.02738</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>1.2212</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.96924</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.78202</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.48494</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.1776</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>1.1542</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>1.23027</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>1.08965</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>1.48672</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>1.21967</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>1.19941</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>1.1542</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.7404299999999999</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.47934</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.40685</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.4129</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42213</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32991</v>
+      </c>
+      <c r="C118" t="n">
+        <v>1.09654</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.9721900000000001</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>1.05676</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.53613</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.52254</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50624</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.53446</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.4978399999999999</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.41008</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.47234</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.38765</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38089</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39203</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33759</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.37047</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35557</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.35923</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.37516</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.37513</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.35908</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.38013</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.42092</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.5512</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.76634</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.7239</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.46122</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.37797</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.4377</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34557</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.39172</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.8575900000000001</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>1.00672</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.6419900000000001</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.83428</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.86993</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.77776</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.65154</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.49683</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.52025</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.6352899999999999</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.34651</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>1.0661</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>1.09192</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>1.37329</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.37091</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>1.02494</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>1.3152</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.89611</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>1.21065</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>1.04469</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.95721</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>1.59082</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.31148</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.51179</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.59824</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.49112</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.51816</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>1.13973</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.9943500000000001</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.9636699999999999</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.98377</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.87975</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.8190700000000001</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.8380700000000001</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.64514</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.91869</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.15964</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>1.07589</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.9052</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.27331</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.51469</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.4566</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.55961</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>1.65797</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.64171</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>1.12177</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>1.22981</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.9621799999999999</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.6745800000000001</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.64205</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.7965599999999999</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.44071</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43473</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.41746</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.3392</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37735</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35443</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33348</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32156</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.51542</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.47531</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.54513</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.43664</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.44331</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.41661</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.39871</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.38901</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38188</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.3612</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.43352</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.44942</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33511</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.36964</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39312</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36613</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.37089</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35312</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.35847</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.3484</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.3629</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35604</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.37999</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39645</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47327</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44987</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.44394</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34795</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39667</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.3516</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36796</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34642</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.6386799999999999</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.66354</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.83815</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.67845</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.63363</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.62187</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.48264</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.30833</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.31499</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.30197</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.50505</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.39499</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.70441</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.9452699999999999</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>1.29983</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.62707</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>1.01274</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>1.37102</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.86277</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.91842</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.7002</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.8442799999999999</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>1.00044</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.98538</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.7176</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.46628</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.38684</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.41333</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.5364800000000001</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.95713</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.8903099999999999</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>1.00293</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>1.60049</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>1.19549</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>1.17716</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>1.00552</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.94467</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.89424</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>1.37247</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>1.29695</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>1.15438</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>1.12236</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>1.20117</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>1.11814</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>1.06982</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>1.59274</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.94167</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>1.62372</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.94024</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.96111</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.9471799999999999</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>1.04861</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.97649</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>1.0812</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.8985299999999999</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.68675</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.6678999999999999</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.50562</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.39028</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34312</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31992</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.94145</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.59148</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.5033</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.47428</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.52973</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.6018600000000001</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.39344</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.58713</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.32716</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.37647</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.35556</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.46639</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.3543</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.31783</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.35557</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.35327</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.31978</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.32997</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.3188</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.32193</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.31999</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.31565</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.37261</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33921</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35749</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.37363</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38871</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.33864</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.36228</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.33572</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.42403</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.34496</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.5917100000000001</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.56697</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.70063</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.9459099999999999</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>1.01609</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.6995800000000001</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>1.11647</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>1.15609</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.67215</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.75667</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>1.03092</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>1.02872</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>1.26277</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.87226</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.95409</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.56889</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.72263</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.48721</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.44196</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.55267</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.8511599999999999</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.99329</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.85854</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.88383</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.90346</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.8362200000000001</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.79371</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.75766</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>1.00235</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>1.06438</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.6365599999999999</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>1.01881</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.95541</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.6727300000000001</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.8663099999999999</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.91346</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.8395</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.94017</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>1.01865</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>1.03912</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.99676</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>1.03024</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>1.68754</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.94343</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.90222</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.85729</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.9376100000000001</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.9747899999999999</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.96965</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.9425399999999999</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.8813099999999999</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.62312</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.45956</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.32799</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.63144</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.31911</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.32189</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31796</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.31811</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.31274</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.58727</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.46868</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.40004</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.36192</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.34312</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.32555</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.3264</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.33371</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.31605</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31717</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31276</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31785</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31403</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.3116</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31274</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.30879</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31136</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.31588</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.31231</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.30847</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31324</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31271</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31645</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32442</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32432</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.3328</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.3261</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.31426</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.31038</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.34204</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.33942</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.22476</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.22019</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.26305</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.21975</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.3039</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.19304</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.24283</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.26034</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.42241</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.50303</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.3602</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.41343</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.19145</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.42902</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.18673</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.5006</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.41493</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.18754</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.32093</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.31998</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.31227</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.34566</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.26982</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.18179</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.22616</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.21518</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.21416</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.17542</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.19441</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.20374</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>0.18438</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.39718</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.32186</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.36762</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.39824</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.52873</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.43784</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.43501</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.37879</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.43362</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.44253</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.5174800000000001</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.38223</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.44964</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.46833</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.40264</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.45628</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.36994</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.38648</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.39953</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39845</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.40986</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46754</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.37094</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39643</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.40002</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.34921</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35501</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35809</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34469</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35529</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.31169</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="C122" t="n">
+        <v>1.03851</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.79925</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.8261799999999999</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.5410700000000001</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.5228400000000001</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.3862</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.39764</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.38471</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.35421</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.33514</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.33776</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.38457</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.36421</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.36287</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.34525</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33985</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.33126</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.33666</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.33996</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.33261</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.32329</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.33261</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33532</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.3388</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.35002</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35201</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34244</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31601</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.23257</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.06655</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04659000000000001</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>0.18219</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04571</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04386</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04571</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04421</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04319</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.04184</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.01412</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.2131</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.05315</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.04345</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.16976</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.06812</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04295</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04272</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.0448</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.04469</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04486</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.01317</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.0423</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04447</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.0419</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.04235</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>0.18031</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04437</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04477</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04229</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04347</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.18073</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.18095</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.04978</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>0.1833</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>0.19543</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>0.20222</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>0.20228</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>0.2047</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.31831</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.32633</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.39361</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.34773</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.35066</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.34331</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.34155</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.3938</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.43489</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.36624</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.35202</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.3663</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.36469</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.33878</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.36724</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.39506</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.37152</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.36974</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.34369</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.33422</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.35468</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.38433</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.36111</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36749</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36598</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33586</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33126</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.3926</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31759</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.40552</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.34937</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32172</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.31483</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31951</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.31252</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.30402</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.30725</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.3023</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.30516</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.30263</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.29656</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.29265</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2988</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.25896</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.25247</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17179</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14841</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.16013</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15937</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23742</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21479</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.27562</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.29055</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.30044</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.30596</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.32028</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.30869</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.30391</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.30645</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.30623</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.30308</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.3076</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32355</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.32432</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.32869</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.37077</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.64191</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.75482</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.59201</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.5655800000000001</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.6099600000000001</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.6638099999999999</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.82025</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.4873</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.35525</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.46521</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.6550900000000001</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.65116</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.7730399999999999</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.52976</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.48056</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.41787</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.41402</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.14101</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.30631</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31936</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.3544</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31818</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.35985</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.62018</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.62764</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.5663400000000001</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.55155</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.48026</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.67655</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79696</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.7449</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.55323</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.68437</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.9637899999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>1.29185</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.7610800000000001</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>1.31406</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>1.288</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.70439</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.6960499999999999</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>1.2719</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.9448</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.66357</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>1.27346</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.67044</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.35228</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.7243999999999999</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.8043899999999999</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.53035</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.7876299999999999</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.78823</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8785700000000001</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.88089</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.5057200000000001</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.41204</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.41609</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.46432</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.2232</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87937</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55135</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.6393099999999999</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.54235</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.50199</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45759</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42591</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43984</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45034</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.39225</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45254</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.42035</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.35372</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.39988</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36503</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38794</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41494</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43395</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34402</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39027</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.34761</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.35319</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.34795</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.35039</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.40499</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.35217</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45064</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.35569</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.39035</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.39991</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.59582</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.43415</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.59623</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.58243</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.66625</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.84363</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.58297</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.55233</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.54987</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>1.31973</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.8929900000000001</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>1.1731</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.1497</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>1.11306</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.48477</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.6606799999999999</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.49101</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.54899</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.48289</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.81938</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.6876</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.5954700000000001</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.53704</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.5013</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.85284</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.7081900000000001</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>1.47211</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.5535399999999999</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.56684</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.43662</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.53864</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.5273</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.5561499999999999</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.57509</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.52646</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.5538999999999999</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.56875</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.52125</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.55365</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.54957</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.48034</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.54143</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.56699</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.66391</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.55468</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.654</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.56823</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.5622699999999999</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.57099</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.5501200000000001</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.53652</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.5226499999999999</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.53342</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.45825</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.38096</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.47335</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.41224</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45201</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.4146</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.3911</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.37454</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.35301</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32927</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.95592</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36057</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.476</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.40682</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.47745</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.53971</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.39151</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.40935</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.38967</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.4061</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.38156</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.3534</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.37611</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33069</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35926</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.34579</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32306</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.39986</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.50007</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.3572</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38768</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34357</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35092</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.3553</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37063</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35772</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36285</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31632</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31347</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33246</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.59812</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.39552</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.5016</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.54253</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.6334500000000001</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.74907</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.93148</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.7227899999999999</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.44997</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.8481599999999999</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.7176</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.80006</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.73138</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.56672</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.69617</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.85541</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.32512</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.45886</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.44722</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.40963</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.3569</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.36113</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.75422</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>1.20581</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.7618200000000001</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.61091</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>1.0011</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.6837300000000001</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.70124</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.55216</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>1.25902</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.64513</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.36876</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.36848</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.38599</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.3845</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.33082</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.36947</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.31443</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35002</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.3262</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.40821</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.38444</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.35462</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.42613</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.40482</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.46592</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.33257</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.41141</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.33934</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.41432</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.7354400000000001</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.4325</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.39611</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.32768</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.39341</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44783</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.33602</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.42043</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35896</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40171</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.40044</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.59674</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="C126" t="n">
+        <v>1.09324</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.77678</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.38779</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.70357</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.79531</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.64977</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.58362</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.45044</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45034</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.50049</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.4399</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43746</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41504</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.42352</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.50054</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43408</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43413</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.39041</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42802</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.45041</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39631</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.4235</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43412</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.40027</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42354</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.3966</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.40249</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.72054</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.4206</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.66427</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.94272</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.7583200000000001</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.5660700000000001</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>1.16732</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.60046</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>1.17301</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.38223</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>1.48829</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>1.00108</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>1.2281</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.74634</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.5257999999999999</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>1.22448</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>1.0571</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.88148</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.8615700000000001</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.83892</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.8317100000000001</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>1.31824</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>1.13462</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.36437</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.52155</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.6959299999999999</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>1.11644</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.62399</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.86707</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.85004</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.72034</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.77391</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.75017</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.9060499999999999</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.93259</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.74734</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.93916</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>1.22558</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.8391900000000001</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.8446900000000001</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.94808</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.80557</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.83086</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>1.20253</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.80787</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.82838</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.9047799999999999</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.77038</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.758</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>1.41131</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.94409</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>1.56419</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>1.3224</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.8447899999999999</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.85976</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.66957</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.38652</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.36963</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33459</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.34094</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32956</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.3247</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.31897</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.43218</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.33907</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.34388</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.3399</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33593</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.32615</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.32941</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.3262</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.3249</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.32411</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.31013</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.32743</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.32615</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.31992</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.31598</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.32012</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.3201</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.31018</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.32511</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.31118</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.3192</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.32048</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.39124</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32505</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.39999</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.37498</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.34993</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33881</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.35467</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33218</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.33456</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.31899</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.39101</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.3362</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.3775</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.32795</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.35788</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.33353</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.31607</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.27469</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.28415</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.31499</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.3107</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>0.7399199999999999</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>0.6692899999999999</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.25531</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.27252</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.35109</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.32492</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.38139</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.35506</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.39943</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.40145</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.31412</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.3084</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.33039</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.34237</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.29556</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.35368</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.27771</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.34051</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.34448</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.35932</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.56456</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.35872</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.39187</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.36166</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.40558</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34363</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.37993</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.3466</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.40025</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.3607</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38491</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.4495</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.39955</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.39356</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.40187</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39771</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.4514</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.43991</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.43927</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.44419</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44427</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.40241</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.39027</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39746</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.3916</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.35973</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.36038</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34804</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34933</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.33969</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.5423</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.38894</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.46868</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.42385</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41592</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.37013</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.38108</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.3802</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.39289</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.37949</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.36952</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.37989</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.35967</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.39072</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.36996</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.37995</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.35027</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.34702</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35526</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34489</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.34006</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.3449700000000001</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.34006</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.3444</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.35478</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.36982</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.37978</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.35965</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.33969</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.33997</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.34032</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32934</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.34697</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.35153</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.37542</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.29261</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.31557</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.3154</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.32436</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.29101</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.30671</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.45679</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.28104</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.5215299999999999</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.36691</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.29611</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.27658</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.27558</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.29916</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.29831</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.3153</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.29857</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.30551</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.39462</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.30511</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.31582</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.29918</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.297</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.32119</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.32377</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.33779</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.30696</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.34371</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.4212</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.56296</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.50306</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.50138</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.62605</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.8659600000000001</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.80889</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.63279</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.40863</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.37566</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.40013</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.5594</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.69133</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.82329</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.8058500000000001</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.68726</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.46291</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.41452</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.398</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.38012</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.36918</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.41951</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.39219</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.43518</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.41738</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.39741</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.40138</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38036</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38532</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.36025</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.34019</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36607</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.41864</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37069</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.5014700000000001</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.38048</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35276</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.3495</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.36023</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35176</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34198</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.34779</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.3458</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.34901</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.34612</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.34902</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.34115</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.34283</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33797</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.33798</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.33983</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33061</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.34275</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.35735</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.34921</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.37642</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.42912</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.37415</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.59699</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.34316</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.38214</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.7563099999999999</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.7555499999999999</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.74427</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.74646</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>1.0747</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>1.07932</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.67671</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.79634</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>1.25877</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.7232799999999999</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>1.24291</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>1.12308</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>1.11581</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>1.18317</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.45777</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.8718400000000001</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.2996</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>1.39026</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.48456</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.87593</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.38679</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.8300700000000001</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.73748</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>1.11543</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>1.09849</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>1.13195</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>1.1453</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>1.14041</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>1.11752</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>1.14198</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.8582799999999999</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>1.17508</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>1.41279</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>1.25653</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>1.29102</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>1.17209</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>1.17984</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>1.18794</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>1.12228</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>1.22222</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.73124</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.7982100000000001</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>1.16592</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>1.1743</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>1.16818</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>1.78579</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>1.24764</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>1.56461</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>1.19783</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>1.34555</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.64459</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.5452400000000001</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.41681</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>1.75475</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>1.21562</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.76928</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.34658</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.34373</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.4213</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.33244</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.35247</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.33023</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.32702</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.33355</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.32609</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.43805</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.8016799999999999</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.35093</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.33298</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.33949</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.36766</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.34423</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.35775</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.33813</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.34165</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32659</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.33391</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.32894</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.3263</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.32743</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.33129</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.33096</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.32605</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32083</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31973</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.32299</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.32635</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.33006</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33517</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.34594</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.34074</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.3439</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.33847</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33873</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.33045</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.34015</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.34189</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.5386299999999999</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.54312</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.34106</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.38966</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.5941799999999999</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.42513</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.44392</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.44656</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.33823</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.29361</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.34223</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.34165</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.29995</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32575</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28308</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.33347</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.33192</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.3221</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.33418</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32848</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33353</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.33944</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.3276</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.33615</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.32487</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.33562</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.33023</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.37346</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.41459</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.69657</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>1.02529</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.86214</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.67584</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.58516</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.40571</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.36901</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.35006</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.42153</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.43083</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.43757</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.41264</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.44922</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.36763</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.36151</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.36781</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.36244</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.37312</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.36204</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.39291</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38553</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37162</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.40289</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35499</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.37992</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.36945</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.36097</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.35025</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.34934</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.3493</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.33957</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35129</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.35532</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.35541</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.35136</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35084</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.34944</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34939</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34624</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.35972</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.3470299999999999</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.34964</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.34947</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33704</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.33957</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.34004</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.3396</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.36929</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32438</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.3383</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.33957</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.34947</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.33665</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.33963</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34504</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.33589</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33633</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.34011</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.32806</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.34853</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.38161</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.34035</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.3802</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.29663</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.33789</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.33021</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.32801</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.33443</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.32475</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.32755</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.32415</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.32141</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.33946</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32601</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32969</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31879</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37108</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.33509</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.40269</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.5932999999999999</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.38687</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.44656</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>1.19465</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.43569</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.37547</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.38434</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.39214</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.34551</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.33183</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.341</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34561</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.39921</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.5634600000000001</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.38927</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35461</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.40023</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.42287</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.35188</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.38632</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34731</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.36029</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.36023</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36226</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.3502</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.56391</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.42454</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.42623</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38363</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.42996</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.40914</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.38576</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.38506</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.6518999999999999</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.83105</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.47185</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.40141</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.45942</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.3934</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.35067</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35096</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35958</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.33988</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.34478</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.3128</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.41059</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37564</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.37071</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.36083</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.35901</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35904</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.36225</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.35885</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.3605</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.35941</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35358</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.36063</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.3608</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35679</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35235</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35977</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.3601</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35977</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.33987</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.37085</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35879</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.3565</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.37946</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36587</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.3799</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35653</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35649</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35113</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35182</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35815</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34973</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.32988</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.35598</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.39956</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.44477</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.36058</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.39394</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.59387</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.32308</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.32239</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.57584</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.31226</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.32867</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.32213</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.5633400000000001</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.20561</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.41796</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.30047</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.32462</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.32287</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.3618</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.30946</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.43011</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.27732</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.33743</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.41686</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.5585</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.42813</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.42042</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.38895</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.7615700000000001</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.79737</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>1.03931</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.54262</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.83802</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.39976</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.31327</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.71138</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.8397</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.65142</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.8760399999999999</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.8250700000000001</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.69957</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>1.14553</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.71858</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.94049</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.58531</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>1.04966</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.38662</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.37207</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.64132</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.44083</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.9928400000000001</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>1.1933</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.93222</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.42975</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.41868</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.37767</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37425</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.3673</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.36015</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34536</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.67215</v>
+      </c>
+      <c r="D133" t="n">
+        <v>1.20891</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.9949600000000001</v>
+      </c>
+      <c r="F133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.41944</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.41843</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.40468</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.41088</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.40856</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.41748</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.3998</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.39545</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.41122</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.40894</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.39336</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.38663</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.41821</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.38681</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.41641</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.3899</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.39973</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.39969</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.41226</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.39983</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.45038</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.44946</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.56037</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.50051</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.45056</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.47898</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.44633</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>1.15836</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>1.75288</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>1.63706</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>1.56926</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>1.76673</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>1.52546</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>1.58111</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.501</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.7601599999999999</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.85714</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.92284</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>1.40369</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>1.79243</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>1.54788</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>1.48859</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>1.41251</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>1.24539</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.93841</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.78343</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>1.18936</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.45824</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.45676</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.5092300000000001</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.5351399999999999</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.66479</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.96141</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.62427</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.81029</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.60723</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.829</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.81264</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>1.34611</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>1.30715</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.96413</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.96528</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>1.13685</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>1.10112</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>1.48307</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>1.59466</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>1.15161</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>1.21307</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.98563</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>1.20139</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.8587100000000001</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.47792</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.47133</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.41936</v>
+      </c>
+      <c r="C134" t="n">
+        <v>1.03445</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.61815</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.47918</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.45801</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.43676</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.42655</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.44836</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.41783</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.40083</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.4577</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39934</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40705</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.39864</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38855</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.37992</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.37487</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35688</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36586</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.37681</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.37125</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.3602</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35984</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36586</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38658</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.39025</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.37959</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.36648</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36138</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35512</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37961</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.43321</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.46054</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.39951</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.50475</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.39437</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.3866</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35163</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.36854</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.47219</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.63212</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.6040599999999999</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.60362</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>1.02853</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.9042</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>1.30965</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>1.12026</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.64109</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.68765</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.69836</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.48088</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.39125</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>1.35677</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.31337</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.33015</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.31465</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32312</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35262</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.36594</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.34962</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.4009</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.4575</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.44512</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.48123</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.47685</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.44242</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.36366</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.43031</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.51209</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.49331</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.56113</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.38327</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.38704</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.40608</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.40263</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34408</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.36543</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37799</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.39925</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.37947</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35508</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.39963</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.38148</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37501</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.36027</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39387</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.37905</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36414</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.33117</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.65728</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.88348</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.53467</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.43075</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.41293</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.37703</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.3505</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.37701</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.39655</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.35622</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.35791</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.35126</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.35744</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.3474100000000001</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.3513</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.34858</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.33144</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.33973</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.34038</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33547</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.34048</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.34548</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.3309</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.33049</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.33747</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.33753</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.3689</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.33714</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.33165</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.33022</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.32768</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.40505</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.34067</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.33225</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.33184</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.30857</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.3331</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.35949</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.30581</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.3112</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.216</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.337</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.32134</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.32756</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.32438</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.26642</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04336</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.33078</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.21388</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.2665</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.27999</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.22104</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.28055</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.29538</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.29298</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.25422</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.2762</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.30671</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.39565</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.28781</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.34191</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.36023</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.33819</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.39239</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.34659</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.41505</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.53755</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.45715</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.4118</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.37754</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.4452</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.43085</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.42527</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.33752</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.5100899999999999</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.38465</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.44865</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.40879</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.39961</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.40388</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.38602</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.42325</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.40682</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.44858</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.36001</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.36488</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.36958</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.37876</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.34925</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.34985</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.34967</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.35011</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.35167</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.32294</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.6142300000000001</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.33827</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.34932</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.35232</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.36386</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.33082</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.3245</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.31942</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.31911</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.31049</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.31027</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.31512</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.31059</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.31096</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.31096</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.3109</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.31664</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.3068</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.30681</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.3093</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.3099</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.30614</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.3068</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.3074</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.3105</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.31136</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.3262</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.20797</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.26712</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.37546</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.26697</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.26095</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.21917</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>0.20274</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.26187</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.19602</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>0.21708</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>0.19606</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>0.23313</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>0.57777</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>0.26995</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>0.25863</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>0.20794</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>0.19633</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>0.22551</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>0.19038</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>0.21372</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>0.19854</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>0.19062</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>0.22165</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.45021</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.35836</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>0.18936</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>0.19872</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>0.18938</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>0.20525</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>0.19582</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>0.20006</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>0.31948</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>0.24528</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.29698</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.28927</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.33505</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.3153</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.33146</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.34746</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.32242</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.33102</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.34498</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.36386</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.34038</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.35818</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.34312</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.33221</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.35612</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.35107</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.35247</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.35756</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.34637</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.35844</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.34806</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.38632</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.6652</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.35695</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.41448</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.358</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.346</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.34904</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.34224</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.34856</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.31452</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.34766</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.30616</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.87747</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.9419999999999999</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.45475</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.5130800000000001</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.4278</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.58273</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.5588</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.43389</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.36745</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.36933</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.36031</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.34266</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.34201</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.33684</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.33463</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.35464</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.43734</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.31495</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.36056</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.34112</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.37479</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.33943</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.35692</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.36075</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.39584</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.6445299999999999</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.39465</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.35202</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.58916</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.33728</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.3769</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.9569</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.95999</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>1.08082</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.9265099999999999</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.7597699999999999</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>1.02018</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.48546</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.44457</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.2941</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.34781</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.15166</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.51412</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.4398</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.38755</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.36318</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.23624</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0.20878</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.5032799999999999</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.5250499999999999</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.36794</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.34966</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.2048</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.35258</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.75207</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.56111</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.40744</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.52437</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.8790800000000001</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>1.58742</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.43083</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.64952</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.5633400000000001</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>1.00418</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.7754</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.77176</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.7808999999999999</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.79076</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.94248</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.5742</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.82398</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.61286</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.85073</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>1.31207</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>1.31708</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>1.34611</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>1.31253</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>1.42194</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>1.5104</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.99211</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.82739</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.88012</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.8771599999999999</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>1.2257</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>1.05957</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.82014</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.38414</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.36491</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.6190399999999999</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.37353</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.33878</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.3302</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.49289</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.6638500000000001</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.48373</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.6199</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.621</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.48671</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.42512</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.4181</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.3839</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.39669</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.39452</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.35116</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.35911</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.34623</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34688</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.28601</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.36506</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.35476</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.34704</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.34514</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.35053</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.36544</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.39261</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.38221</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.39957</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.82265</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.69064</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.6340800000000001</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.59334</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.48647</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.5538099999999999</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.51709</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.51375</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.37549</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.85046</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.94101</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.85362</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.9438300000000001</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>1.33615</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>1.33082</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.86466</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.88263</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.61698</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.46781</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.4709</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.52211</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.41688</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.24642</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.47793</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.32292</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.46963</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.46574</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.4148</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.55003</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>1.14642</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.74749</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.45885</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.47148</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.43153</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.43834</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.42868</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.4422</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.43164</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.44669</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.49536</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.48924</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.49425</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.45426</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.46653</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.39213</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.39368</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.37298</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.41103</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.46383</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.49496</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.56845</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.94682</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.89276</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.56767</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.49568</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>1.02366</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.71909</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.59548</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.9440700000000001</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.75718</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.46959</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.47341</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.46096</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.41653</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.47542</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.36639</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.3773</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.3415899999999999</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.34049</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.33999</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.37038</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.44277</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.42443</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.40832</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.39816</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.3873</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.3933</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.35178</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.37476</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.39132</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.36658</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.35396</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.35991</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.35302</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.34957</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.36539</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.35039</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.3492</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.34566</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34651</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.34662</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.34713</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.35914</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.33686</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.36913</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.36004</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.38163</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35942</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.54926</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.59323</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.38444</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.5792</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.87383</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>1.11495</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>1.63724</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.71086</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.8269099999999999</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.8661599999999999</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.81548</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.78801</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.82178</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.80038</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.78984</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.793</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.34525</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>1.24588</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.49054</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.78347</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.5385700000000001</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.79196</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.80018</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>1.64863</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.7820199999999999</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.6544800000000001</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.79591</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.7618200000000001</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.79571</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>1.11073</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>1.27773</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>1.30026</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>1.34778</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>1.41461</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>1.39764</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>1.46737</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>1.47982</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>1.45779</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>1.01803</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.9090499999999999</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.86874</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.48207</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>1.09263</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.84489</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.9319500000000001</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.79243</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.7093200000000001</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.6981000000000001</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.70921</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.66603</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.42422</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.6862200000000001</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.55769</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.40189</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.45847</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.59733</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.38014</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.6717799999999999</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.6335299999999999</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.32409</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.37271</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.36288</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.36869</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34704</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.7028799999999999</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.40117</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.40122</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.39188</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.38075</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.36014</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.37554</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37442</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37864</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.3773</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36916</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36692</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36153</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.36004</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35978</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.3604</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.35586</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32884</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35618</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.35106</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.34723</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.35016</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.36014</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.37103</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.39959</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.37577</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.36966</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.37162</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.40344</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.43552</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.38081</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.7048</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.54249</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.72078</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.59981</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.59901</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.5159</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>1.74461</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>1.74625</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.8717200000000001</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.7343500000000001</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.8700399999999999</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.8020900000000001</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.87803</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.8608300000000001</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.86097</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.35301</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>1.0662</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>1.08519</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.83773</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.5116700000000001</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.33922</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.35268</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.60621</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.3027</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.62824</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.7045</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.68601</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.75867</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>1.29345</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>1.29553</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>1.57737</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>1.31635</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>1.58103</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>1.56268</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>1.59467</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>1.42172</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>1.34647</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.94869</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.9291799999999999</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>1.62367</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>1.69708</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>1.33175</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>1.33334</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>1.15578</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>1.60787</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>1.69852</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>1.67346</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>1.09234</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>1.07657</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.79911</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>1.30212</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>1.28065</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>1.55669</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>1.3237</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>1.32549</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.3983</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.68786</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.6716299999999999</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.66161</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.39801</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.36946</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.37507</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.27083</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.37605</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.36562</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.37042</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.35664</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.34933</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.34988</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.3465</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.35083</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.6193500000000001</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.35243</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.3460299999999999</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.40685</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.36315</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.35206</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.3586</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.34378</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.34871</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.34579</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.34393</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.34668</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.34261</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.34162</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.35192</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.33589</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.36383</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.45421</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.35154</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.33305</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.32763</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.33313</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.31891</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.35826</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.60953</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.92783</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.7375499999999999</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.66742</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.69377</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.85124</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.88106</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.97923</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.59787</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.47606</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>1.26377</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>1.04543</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>1.00669</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.72515</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.5190399999999999</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.19231</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.43687</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.6461</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>1.39466</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.20273</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.70924</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.24218</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.71146</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.78738</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.7036</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.35287</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.8058099999999999</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.55223</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.45476</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.87982</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.68925</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.59138</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.81828</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.65924</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.7874800000000001</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.8772300000000001</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.9340499999999999</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.79223</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.8024600000000001</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.79565</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.7839299999999999</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.7945399999999999</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>1.12564</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>1.16153</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>1.07228</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>1.09144</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>1.27604</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>1.02887</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>1.06671</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.85327</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.83374</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.85087</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.89167</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.89471</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.87586</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.98498</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.636</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.60037</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.54404</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.5225700000000001</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.42059</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.37855</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.37539</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.35017</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1.34514</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.9564199999999999</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.97929</v>
+      </c>
+      <c r="F142" t="n">
+        <v>1.28803</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.80145</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.43303</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.46055</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.37308</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.39257</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.3814</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.37864</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.36486</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.37856</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.37353</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.38209</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.38283</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.3798</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.37533</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.37406</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.36654</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.3729</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.3722</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.36892</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.36771</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.35028</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.38028</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.36152</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.65885</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.36654</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.35043</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.33728</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.33747</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.51877</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.61922</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.62194</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.58536</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.7565599999999999</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.63647</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.76203</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>1.37531</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.8371900000000001</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.92663</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>1.03927</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>1.02635</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.92161</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>1.13313</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.8689199999999999</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.51178</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>1.23367</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.47757</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.42779</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.9113</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.57148</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.67099</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.8917200000000001</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.61919</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.41173</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.4655</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.55065</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.9700299999999999</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.79488</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.62058</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>1.32278</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.9068099999999999</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.8846799999999999</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>1.48996</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>1.26144</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>1.07525</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.94088</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.9149700000000001</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.9193600000000001</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.9122400000000001</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.9345399999999999</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.93662</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.97823</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>1.45371</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>1.50432</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>1.61742</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.89097</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.9131699999999999</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.89686</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.93684</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>1.78674</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>1.13606</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.65086</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.6287200000000001</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.49364</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.36033</v>
+      </c>
+      <c r="C143" t="n">
+        <v>1.02494</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.66773</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.6693</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.46223</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.48125</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.48481</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.45624</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.4715299999999999</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.41963</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.45126</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.45172</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.37331</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.41319</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.41279</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35014</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.3335</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.35728</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.35037</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.34577</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.34345</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.36451</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.3527</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.40502</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.37594</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.3497</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.36505</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.3769</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.41585</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.40192</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.4186</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.39556</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.36447</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.4089</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.7893300000000001</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.61027</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.9414</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>1.24386</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.87499</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.94337</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.408</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.57935</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.55011</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.43239</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.5365800000000001</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>1.23063</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.3594</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.8719600000000001</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.7435499999999999</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.45625</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.39675</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.37686</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.42682</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.42483</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.52416</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.36129</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.59656</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.5595399999999999</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.74963</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.5670299999999999</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.47441</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.90199</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.79332</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.80548</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.8303400000000001</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.84635</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.61252</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.58038</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.55741</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.5739299999999999</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.58113</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.59621</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.66399</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.6650499999999999</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.5504199999999999</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.66888</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.66632</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.96197</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.69512</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.5803700000000001</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.6005900000000001</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.5807100000000001</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.5431</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.54086</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.679</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.6459400000000001</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.7197100000000001</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.58853</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.53764</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.48334</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.46479</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.4085299999999999</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.4097</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.38406</v>
       </c>
     </row>
   </sheetData>
